--- a/internal_doc/07.版本报告/2.8版本特性列表.xlsx
+++ b/internal_doc/07.版本报告/2.8版本特性列表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="158">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -626,6 +626,38 @@
   </si>
   <si>
     <t>何嘉文、黄伟钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:00 - 10:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:40 - 11:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30 - 12:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:00 - 13:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:40 - 14:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:30 - 15:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:20 - 16:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:10 - 16:40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -741,10 +773,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2147,7 +2179,7 @@
   <cols>
     <col min="1" max="1" width="21.375" customWidth="1"/>
     <col min="2" max="2" width="36.25" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
@@ -2176,8 +2208,8 @@
       <c r="B2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="5">
-        <v>42775</v>
+      <c r="C2" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>126</v>
@@ -2193,8 +2225,8 @@
       <c r="B3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="6">
-        <v>42775</v>
+      <c r="C3" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>130</v>
@@ -2210,8 +2242,8 @@
       <c r="B4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="6">
-        <v>42776</v>
+      <c r="C4" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>132</v>
@@ -2227,8 +2259,8 @@
       <c r="B5" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="6">
-        <v>42776</v>
+      <c r="C5" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>147</v>
@@ -2244,8 +2276,8 @@
       <c r="B6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="6">
-        <v>42779</v>
+      <c r="C6" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>149</v>
@@ -2261,8 +2293,8 @@
       <c r="B7" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="6">
-        <v>42779</v>
+      <c r="C7" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>142</v>
@@ -2278,8 +2310,8 @@
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="6">
-        <v>42780</v>
+      <c r="C8" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>137</v>
@@ -2295,8 +2327,8 @@
       <c r="B9" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="6">
-        <v>42780</v>
+      <c r="C9" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>148</v>
